--- a/ig/mc-add-profils-dp/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-dp-practitioner.xlsx
@@ -39,7 +39,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>ASDPPractitionerProfile</t>
+    <t>AsDpPractitionerProfile</t>
   </si>
   <si>
     <t>Title</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T08:42:11+00:00</t>
+    <t>2023-05-17T18:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil créé à partir de as-practitioner dans le contexte de l'Annuaire Santé pour décrire les données d'identification pérennes d’une personne physique, qui travaille en tant que professionnel (professionnel enregistré dans RPPS ou ADELI), personnel autorisé ou personnel d’établissement, dans les domaines sanitaire, médico-social et social.</t>
+    <t>Profil créé à partir de as-practitioner dans le contexte des données en libre accès.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -445,10 +445,10 @@
     <t>Nationalité du professionnel</t>
   </si>
   <si>
-    <t>Practitioner.extension:as-ext-practitioner-authorization</t>
-  </si>
-  <si>
-    <t>as-ext-practitioner-authorization</t>
+    <t>Practitioner.extension:as-ext-frpractitioner-authorization</t>
+  </si>
+  <si>
+    <t>as-ext-frpractitioner-authorization</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-authorization}
@@ -590,7 +590,7 @@
     <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>Synonymes MOS : typeIdNat_PP,
+    <t>Synonyme : typeIdNat_PP,
 Les codes ADELI, RPPS et IDNPS proviennent du system  http://interopsante.org/fhir/CodeSystem/fr-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
   </si>
   <si>
@@ -782,7 +782,8 @@
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>Synonyme MOS : idPP</t>
+    <t>Synonyme : idPP
+ Personne/Identifiant PP si l’instance correspond à un identifiant RPPS ou ADELI, sinon Personne/identification nationale PP.</t>
   </si>
   <si>
     <t>123456</t>
@@ -986,7 +987,7 @@
     <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the start of the name.</t>
   </si>
   <si>
-    <t>Synonyme MOS : civilite</t>
+    <t>Synonyme : civilite</t>
   </si>
   <si>
     <t>Civilités des personnes physiques du RASS</t>
@@ -1078,7 +1079,7 @@
     <t>Les BALs MSS de type PER rattachées seulement à l'identifiant du professionnel de Santé.</t>
   </si>
   <si>
-    <t>Synonyme MOS : boiteLettreMSS</t>
+    <t>Synonyme : boiteLettreMSS</t>
   </si>
   <si>
     <t>Practitioner.telecom:mailbox-mss.id</t>
@@ -1235,7 +1236,7 @@
     <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
   </si>
   <si>
-    <t>Synonyme MOS : adresseCorrespondance</t>
+    <t>Synonyme : adresseCorrespondance</t>
   </si>
   <si>
     <t>The home/mailing address of the practitioner is often required for employee administration purposes, and also for some rostering services where the start point (practitioners home) can be used in calculations.</t>
@@ -1250,7 +1251,7 @@
     <t>Administrative Gender - the gender that the person is considered to have for administration and record keeping purposes.</t>
   </si>
   <si>
-    <t>Synonyme MOS : sexeAdministratif</t>
+    <t>Synonyme : sexeAdministratif</t>
   </si>
   <si>
     <t>Needed to address the person correctly.</t>
@@ -1275,7 +1276,7 @@
     <t>The date of birth for the practitioner.</t>
   </si>
   <si>
-    <t>Synonyme MOS : dateNaissance</t>
+    <t>Synonyme : dateNaissance</t>
   </si>
   <si>
     <t>Needed for identification.</t>
@@ -1912,7 +1913,7 @@
     <t>A concept that may be defined by a formal reference to a terminology or ontology or may be provided by text.</t>
   </si>
   <si>
-    <t>Synonyme MOS : langueParlee</t>
+    <t>Synonyme : langueParlee</t>
   </si>
   <si>
     <t>Knowing which language a practitioner speaks can help in facilitating communication with patients.</t>
@@ -5563,7 +5564,7 @@
         <v>72</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>71</v>
@@ -5665,7 +5666,7 @@
         <v>72</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>71</v>
@@ -6387,7 +6388,7 @@
         <v>72</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>71</v>
@@ -6797,7 +6798,7 @@
         <v>72</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>71</v>
@@ -6899,7 +6900,7 @@
         <v>72</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>71</v>
@@ -21105,7 +21106,7 @@
         <v>72</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>71</v>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:21:34+00:00</t>
+    <t>2023-05-17T18:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:27:08+00:00</t>
+    <t>2023-05-23T08:43:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil créé à partir de as-practitioner dans le contexte des données en libre accès.</t>
+    <t>Profil applicatif créé à partir du profil générique as-practitioner dans le contexte des données en libre accès de l’Annuaire Santé.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -5978,7 +5978,7 @@
         <v>72</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>71</v>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T08:43:56+00:00</t>
+    <t>2023-05-23T08:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
